--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_maule.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_maule.xlsx
@@ -404,7 +404,7 @@
         <v>26.91967749553014</v>
       </c>
       <c r="D2">
-        <v>1.639111297885517</v>
+        <v>2.933498268184067</v>
       </c>
       <c r="E2">
         <v>21.17214705056591</v>
@@ -429,7 +429,7 @@
         <v>27.71508089427164</v>
       </c>
       <c r="D3">
-        <v>1.659072457885123</v>
+        <v>3.071294382866804</v>
       </c>
       <c r="E3">
         <v>20.31485545272398</v>
@@ -454,7 +454,7 @@
         <v>23.38503494119652</v>
       </c>
       <c r="D4">
-        <v>1.20348717948718</v>
+        <v>1.674850128461319</v>
       </c>
       <c r="E4">
         <v>32.61031465276484</v>
@@ -479,7 +479,7 @@
         <v>32.63920325939339</v>
       </c>
       <c r="D5">
-        <v>1.381488430268918</v>
+        <v>2.515945330296128</v>
       </c>
       <c r="E5">
         <v>23.05672268907563</v>
@@ -504,7 +504,7 @@
         <v>30.8788143935251</v>
       </c>
       <c r="D6">
-        <v>1.893646766426759</v>
+        <v>4.560099750623442</v>
       </c>
       <c r="E6">
         <v>14.35089916793415</v>
@@ -529,7 +529,7 @@
         <v>25.90299277605779</v>
       </c>
       <c r="D7">
-        <v>1.50787784477728</v>
+        <v>2.474305777210342</v>
       </c>
       <c r="E7">
         <v>24.30000775614674</v>
@@ -554,7 +554,7 @@
         <v>22.18754644077872</v>
       </c>
       <c r="D8">
-        <v>1.599096958174905</v>
+        <v>2.478453038674033</v>
       </c>
       <c r="E8">
         <v>24.8239919539179</v>
@@ -579,7 +579,7 @@
         <v>27.99958411312123</v>
       </c>
       <c r="D9">
-        <v>1.446315789473684</v>
+        <v>2.43062926459439</v>
       </c>
       <c r="E9">
         <v>24.32382591590853</v>
@@ -604,7 +604,7 @@
         <v>28.98612523370617</v>
       </c>
       <c r="D10">
-        <v>1.518352507595</v>
+        <v>2.711884006404554</v>
       </c>
       <c r="E10">
         <v>22.23233002412688</v>
@@ -629,7 +629,7 @@
         <v>25.02072232089994</v>
       </c>
       <c r="D11">
-        <v>1.629050925925926</v>
+        <v>2.749918593292087</v>
       </c>
       <c r="E11">
         <v>22.53283439724117</v>
@@ -654,7 +654,7 @@
         <v>28.19193273656362</v>
       </c>
       <c r="D12">
-        <v>1.375249202551834</v>
+        <v>2.246072446072446</v>
       </c>
       <c r="E12">
         <v>25.777954969889</v>
@@ -679,7 +679,7 @@
         <v>29.18838421444527</v>
       </c>
       <c r="D13">
-        <v>1.278134665714965</v>
+        <v>2.038709677419355</v>
       </c>
       <c r="E13">
         <v>27.51958224543081</v>
@@ -704,7 +704,7 @@
         <v>24.92433414043584</v>
       </c>
       <c r="D14">
-        <v>1.474341811691209</v>
+        <v>2.330864197530864</v>
       </c>
       <c r="E14">
         <v>25.56357078449053</v>
@@ -729,7 +729,7 @@
         <v>26.69621990577586</v>
       </c>
       <c r="D15">
-        <v>1.710442410494758</v>
+        <v>3.147803240402861</v>
       </c>
       <c r="E15">
         <v>20.04752178569548</v>
@@ -754,7 +754,7 @@
         <v>23.97091108671789</v>
       </c>
       <c r="D16">
-        <v>1.443740095087163</v>
+        <v>2.207815813389882</v>
       </c>
       <c r="E16">
         <v>26.75907911802854</v>
@@ -779,7 +779,7 @@
         <v>24.9780316344464</v>
       </c>
       <c r="D17">
-        <v>1.455708346658139</v>
+        <v>2.287437185929648</v>
       </c>
       <c r="E17">
         <v>25.91483266050267</v>
@@ -804,7 +804,7 @@
         <v>27.76881975402321</v>
       </c>
       <c r="D18">
-        <v>1.553029559069037</v>
+        <v>2.730639730639731</v>
       </c>
       <c r="E18">
         <v>22.27714203288777</v>
@@ -829,7 +829,7 @@
         <v>27.22435707951522</v>
       </c>
       <c r="D19">
-        <v>1.479553903345725</v>
+        <v>2.477480776272428</v>
       </c>
       <c r="E19">
         <v>24.08501631537173</v>
@@ -854,7 +854,7 @@
         <v>26.11243072050673</v>
       </c>
       <c r="D20">
-        <v>1.662498354613663</v>
+        <v>2.937892533147243</v>
       </c>
       <c r="E20">
         <v>21.25376971374896</v>
@@ -879,7 +879,7 @@
         <v>24.25135764158262</v>
       </c>
       <c r="D21">
-        <v>1.594113282216176</v>
+        <v>2.598790322580645</v>
       </c>
       <c r="E21">
         <v>23.64607170099161</v>
@@ -904,7 +904,7 @@
         <v>26.28860810268753</v>
       </c>
       <c r="D22">
-        <v>1.551458576429405</v>
+        <v>2.620073568050447</v>
       </c>
       <c r="E22">
         <v>23.2080246348974</v>
@@ -929,7 +929,7 @@
         <v>23.10456342076895</v>
       </c>
       <c r="D23">
-        <v>1.368239921337267</v>
+        <v>2.000718907260963</v>
       </c>
       <c r="E23">
         <v>28.87689433257214</v>
@@ -954,7 +954,7 @@
         <v>26.90117052606401</v>
       </c>
       <c r="D24">
-        <v>1.572472966619652</v>
+        <v>2.725320839274801</v>
       </c>
       <c r="E24">
         <v>22.42924894684419</v>
@@ -979,7 +979,7 @@
         <v>29.17743752899847</v>
       </c>
       <c r="D25">
-        <v>1.478682740370479</v>
+        <v>2.600758489915532</v>
       </c>
       <c r="E25">
         <v>22.93792012653223</v>
@@ -1004,7 +1004,7 @@
         <v>26.3900806590012</v>
       </c>
       <c r="D26">
-        <v>1.55739676600294</v>
+        <v>2.64412932501418</v>
       </c>
       <c r="E26">
         <v>23.03130062183205</v>
@@ -1029,7 +1029,7 @@
         <v>27.571072319202</v>
       </c>
       <c r="D27">
-        <v>1.478977133021883</v>
+        <v>2.497301336876194</v>
       </c>
       <c r="E27">
         <v>23.8901011704027</v>
@@ -1054,7 +1054,7 @@
         <v>28.11289842120942</v>
       </c>
       <c r="D28">
-        <v>1.425931825422109</v>
+        <v>2.380007089684509</v>
       </c>
       <c r="E28">
         <v>24.69687021230029</v>
@@ -1079,7 +1079,7 @@
         <v>29.94252693068685</v>
       </c>
       <c r="D29">
-        <v>1.48699388222108</v>
+        <v>2.680444481858742</v>
       </c>
       <c r="E29">
         <v>22.30630562962406</v>
@@ -1104,7 +1104,7 @@
         <v>28.44968268359021</v>
       </c>
       <c r="D30">
-        <v>1.422491617229817</v>
+        <v>2.389514731369151</v>
       </c>
       <c r="E30">
         <v>24.57410562180579</v>
@@ -1129,7 +1129,7 @@
         <v>27.50261858446805</v>
       </c>
       <c r="D31">
-        <v>1.551479976784678</v>
+        <v>2.706215833164608</v>
       </c>
       <c r="E31">
         <v>22.4694053955689</v>

--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_maule.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_maule.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>26.91967749553014</v>
+      </c>
+      <c r="C2">
         <v>34.08899234220558</v>
-      </c>
-      <c r="C2">
-        <v>26.91967749553014</v>
       </c>
       <c r="D2">
         <v>2.933498268184067</v>
       </c>
       <c r="E2">
-        <v>21.17214705056591</v>
+        <v>16.71939624286055</v>
       </c>
       <c r="F2">
-        <v>62.10845670657352</v>
+        <v>62.10845670657353</v>
       </c>
       <c r="G2">
-        <v>16.71939624286055</v>
+        <v>21.17214705056592</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>27.71508089427164</v>
+      </c>
+      <c r="C3">
         <v>32.55956203933083</v>
-      </c>
-      <c r="C3">
-        <v>27.71508089427164</v>
       </c>
       <c r="D3">
         <v>3.071294382866804</v>
       </c>
       <c r="E3">
-        <v>20.31485545272398</v>
+        <v>17.2922431065738</v>
       </c>
       <c r="F3">
         <v>62.39290144070222</v>
       </c>
       <c r="G3">
-        <v>17.2922431065738</v>
+        <v>20.31485545272398</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>23.38503494119652</v>
+      </c>
+      <c r="C4">
         <v>59.7068348389296</v>
-      </c>
-      <c r="C4">
-        <v>23.38503494119652</v>
       </c>
       <c r="D4">
         <v>1.674850128461319</v>
       </c>
       <c r="E4">
-        <v>32.61031465276484</v>
+        <v>12.77229566188792</v>
       </c>
       <c r="F4">
         <v>54.61738968534723</v>
       </c>
       <c r="G4">
-        <v>12.77229566188792</v>
+        <v>32.61031465276484</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>32.63920325939339</v>
+      </c>
+      <c r="C5">
         <v>39.74649162516976</v>
-      </c>
-      <c r="C5">
-        <v>32.63920325939339</v>
       </c>
       <c r="D5">
         <v>2.515945330296128</v>
       </c>
       <c r="E5">
-        <v>23.05672268907563</v>
+        <v>18.93382352941176</v>
       </c>
       <c r="F5">
         <v>58.0094537815126</v>
       </c>
       <c r="G5">
-        <v>18.93382352941176</v>
+        <v>23.05672268907563</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>30.8788143935251</v>
+      </c>
+      <c r="C6">
         <v>21.92934485398666</v>
-      </c>
-      <c r="C6">
-        <v>30.8788143935251</v>
       </c>
       <c r="D6">
         <v>4.560099750623442</v>
       </c>
       <c r="E6">
-        <v>14.35089916793415</v>
+        <v>20.20756911514718</v>
       </c>
       <c r="F6">
         <v>65.44153171691867</v>
       </c>
       <c r="G6">
-        <v>20.20756911514718</v>
+        <v>14.35089916793415</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>25.90299277605779</v>
+      </c>
+      <c r="C7">
         <v>40.41537667698659</v>
-      </c>
-      <c r="C7">
-        <v>25.90299277605779</v>
       </c>
       <c r="D7">
         <v>2.474305777210342</v>
       </c>
       <c r="E7">
-        <v>24.30000775614674</v>
+        <v>15.57434266656325</v>
       </c>
       <c r="F7">
         <v>60.12564957728999</v>
       </c>
       <c r="G7">
-        <v>15.57434266656325</v>
+        <v>24.30000775614674</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>22.18754644077872</v>
+      </c>
+      <c r="C8">
         <v>40.3477485510477</v>
-      </c>
-      <c r="C8">
-        <v>22.18754644077872</v>
       </c>
       <c r="D8">
         <v>2.478453038674033</v>
       </c>
       <c r="E8">
-        <v>24.8239919539179</v>
+        <v>13.65090975587455</v>
       </c>
       <c r="F8">
-        <v>61.52509829020757</v>
+        <v>61.52509829020755</v>
       </c>
       <c r="G8">
-        <v>13.65090975587456</v>
+        <v>24.82399195391789</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>27.99958411312123</v>
+      </c>
+      <c r="C9">
         <v>41.14160948222084</v>
-      </c>
-      <c r="C9">
-        <v>27.99958411312123</v>
       </c>
       <c r="D9">
         <v>2.43062926459439</v>
       </c>
       <c r="E9">
-        <v>24.32382591590853</v>
+        <v>16.55397098598476</v>
       </c>
       <c r="F9">
-        <v>59.1222030981067</v>
+        <v>59.12220309810672</v>
       </c>
       <c r="G9">
-        <v>16.55397098598475</v>
+        <v>24.32382591590854</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.98612523370617</v>
+      </c>
+      <c r="C10">
         <v>36.87473349296421</v>
-      </c>
-      <c r="C10">
-        <v>28.98612523370617</v>
       </c>
       <c r="D10">
         <v>2.711884006404554</v>
       </c>
       <c r="E10">
-        <v>22.23233002412688</v>
+        <v>17.47616975833564</v>
       </c>
       <c r="F10">
         <v>60.29150021753748</v>
       </c>
       <c r="G10">
-        <v>17.47616975833564</v>
+        <v>22.23233002412688</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>25.02072232089994</v>
+      </c>
+      <c r="C11">
         <v>36.36471284783896</v>
-      </c>
-      <c r="C11">
-        <v>25.02072232089994</v>
       </c>
       <c r="D11">
         <v>2.749918593292087</v>
       </c>
       <c r="E11">
-        <v>22.53283439724117</v>
+        <v>15.50370533421381</v>
       </c>
       <c r="F11">
         <v>61.96346026854501</v>
       </c>
       <c r="G11">
-        <v>15.50370533421381</v>
+        <v>22.53283439724117</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>28.19193273656362</v>
+      </c>
+      <c r="C12">
         <v>44.52216141775088</v>
-      </c>
-      <c r="C12">
-        <v>28.19193273656362</v>
       </c>
       <c r="D12">
         <v>2.246072446072446</v>
       </c>
       <c r="E12">
-        <v>25.777954969889</v>
+        <v>16.32289065614705</v>
       </c>
       <c r="F12">
         <v>57.89915437396395</v>
       </c>
       <c r="G12">
-        <v>16.32289065614705</v>
+        <v>25.777954969889</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>29.18838421444527</v>
+      </c>
+      <c r="C13">
         <v>49.05063291139241</v>
-      </c>
-      <c r="C13">
-        <v>29.18838421444527</v>
       </c>
       <c r="D13">
         <v>2.038709677419355</v>
       </c>
       <c r="E13">
-        <v>27.51958224543081</v>
+        <v>16.37597911227154</v>
       </c>
       <c r="F13">
         <v>56.10443864229765</v>
       </c>
       <c r="G13">
-        <v>16.37597911227154</v>
+        <v>27.51958224543081</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>24.92433414043584</v>
+      </c>
+      <c r="C14">
         <v>42.90254237288136</v>
-      </c>
-      <c r="C14">
-        <v>24.92433414043584</v>
       </c>
       <c r="D14">
         <v>2.330864197530864</v>
       </c>
       <c r="E14">
-        <v>25.56357078449053</v>
+        <v>14.8512173128945</v>
       </c>
       <c r="F14">
         <v>59.58521190261497</v>
       </c>
       <c r="G14">
-        <v>14.8512173128945</v>
+        <v>25.56357078449053</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>26.69621990577586</v>
+      </c>
+      <c r="C15">
         <v>31.76818637088697</v>
-      </c>
-      <c r="C15">
-        <v>26.69621990577586</v>
       </c>
       <c r="D15">
         <v>3.147803240402861</v>
       </c>
       <c r="E15">
-        <v>20.04752178569548</v>
+        <v>16.84682417524536</v>
       </c>
       <c r="F15">
         <v>63.10565403905917</v>
       </c>
       <c r="G15">
-        <v>16.84682417524536</v>
+        <v>20.04752178569548</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>23.97091108671789</v>
+      </c>
+      <c r="C16">
         <v>45.29363336992316</v>
-      </c>
-      <c r="C16">
-        <v>23.97091108671789</v>
       </c>
       <c r="D16">
         <v>2.207815813389882</v>
       </c>
       <c r="E16">
-        <v>26.75907911802854</v>
+        <v>14.16180285343709</v>
       </c>
       <c r="F16">
-        <v>59.07911802853438</v>
+        <v>59.07911802853437</v>
       </c>
       <c r="G16">
-        <v>14.1618028534371</v>
+        <v>26.75907911802853</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>24.9780316344464</v>
+      </c>
+      <c r="C17">
         <v>43.71704745166959</v>
-      </c>
-      <c r="C17">
-        <v>24.9780316344464</v>
       </c>
       <c r="D17">
         <v>2.287437185929648</v>
       </c>
       <c r="E17">
-        <v>25.91483266050267</v>
+        <v>14.80661544471937</v>
       </c>
       <c r="F17">
         <v>59.27855189477797</v>
       </c>
       <c r="G17">
-        <v>14.80661544471937</v>
+        <v>25.91483266050267</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>27.76881975402321</v>
+      </c>
+      <c r="C18">
         <v>36.62145499383477</v>
-      </c>
-      <c r="C18">
-        <v>27.76881975402321</v>
       </c>
       <c r="D18">
         <v>2.730639730639731</v>
       </c>
       <c r="E18">
-        <v>22.27714203288777</v>
+        <v>16.89200884700452</v>
       </c>
       <c r="F18">
-        <v>60.83084912010769</v>
+        <v>60.83084912010771</v>
       </c>
       <c r="G18">
-        <v>16.89200884700452</v>
+        <v>22.27714203288778</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>27.22435707951522</v>
+      </c>
+      <c r="C19">
         <v>40.36358261897724</v>
-      </c>
-      <c r="C19">
-        <v>27.22435707951522</v>
       </c>
       <c r="D19">
         <v>2.477480776272428</v>
       </c>
       <c r="E19">
-        <v>24.08501631537173</v>
+        <v>16.24481876708704</v>
       </c>
       <c r="F19">
         <v>59.67016491754124</v>
       </c>
       <c r="G19">
-        <v>16.24481876708704</v>
+        <v>24.08501631537173</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>26.11243072050673</v>
+      </c>
+      <c r="C20">
         <v>34.03800475059383</v>
-      </c>
-      <c r="C20">
-        <v>26.11243072050673</v>
       </c>
       <c r="D20">
         <v>2.937892533147243</v>
       </c>
       <c r="E20">
-        <v>21.25376971374896</v>
+        <v>16.30493894299699</v>
       </c>
       <c r="F20">
         <v>62.44129134325407</v>
       </c>
       <c r="G20">
-        <v>16.30493894299699</v>
+        <v>21.25376971374896</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>24.25135764158262</v>
+      </c>
+      <c r="C21">
         <v>38.47944142746315</v>
-      </c>
-      <c r="C21">
-        <v>24.25135764158262</v>
       </c>
       <c r="D21">
         <v>2.598790322580645</v>
       </c>
       <c r="E21">
-        <v>23.64607170099161</v>
+        <v>14.90274599542334</v>
       </c>
       <c r="F21">
         <v>61.45118230358506</v>
       </c>
       <c r="G21">
-        <v>14.90274599542334</v>
+        <v>23.64607170099161</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>26.28860810268753</v>
+      </c>
+      <c r="C22">
         <v>38.16686722823907</v>
-      </c>
-      <c r="C22">
-        <v>26.28860810268753</v>
       </c>
       <c r="D22">
         <v>2.620073568050447</v>
       </c>
       <c r="E22">
-        <v>23.2080246348974</v>
+        <v>15.98524345254428</v>
       </c>
       <c r="F22">
         <v>60.8067319125583</v>
       </c>
       <c r="G22">
-        <v>15.98524345254428</v>
+        <v>23.2080246348974</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>23.10456342076895</v>
+      </c>
+      <c r="C23">
         <v>49.98203377650018</v>
-      </c>
-      <c r="C23">
-        <v>23.10456342076895</v>
       </c>
       <c r="D23">
         <v>2.000718907260963</v>
       </c>
       <c r="E23">
-        <v>28.87689433257214</v>
+        <v>13.34855719327382</v>
       </c>
       <c r="F23">
         <v>57.77454847415404</v>
       </c>
       <c r="G23">
-        <v>13.34855719327382</v>
+        <v>28.87689433257214</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>26.90117052606401</v>
+      </c>
+      <c r="C24">
         <v>36.69292751109982</v>
-      </c>
-      <c r="C24">
-        <v>26.90117052606401</v>
       </c>
       <c r="D24">
         <v>2.725320839274801</v>
       </c>
       <c r="E24">
-        <v>22.42924894684419</v>
+        <v>16.44385148903896</v>
       </c>
       <c r="F24">
         <v>61.12689956411685</v>
       </c>
       <c r="G24">
-        <v>16.44385148903896</v>
+        <v>22.42924894684419</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>29.17743752899847</v>
+      </c>
+      <c r="C25">
         <v>38.45032146881422</v>
-      </c>
-      <c r="C25">
-        <v>29.17743752899847</v>
       </c>
       <c r="D25">
         <v>2.600758489915532</v>
       </c>
       <c r="E25">
-        <v>22.93792012653223</v>
+        <v>17.40608936338474</v>
       </c>
       <c r="F25">
         <v>59.65599051008304</v>
       </c>
       <c r="G25">
-        <v>17.40608936338474</v>
+        <v>22.93792012653223</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>26.3900806590012</v>
+      </c>
+      <c r="C26">
         <v>37.81963274412219</v>
-      </c>
-      <c r="C26">
-        <v>26.3900806590012</v>
       </c>
       <c r="D26">
         <v>2.64412932501418</v>
       </c>
       <c r="E26">
+        <v>16.07096201076449</v>
+      </c>
+      <c r="F26">
+        <v>60.89773736740347</v>
+      </c>
+      <c r="G26">
         <v>23.03130062183205</v>
-      </c>
-      <c r="F26">
-        <v>60.89773736740346</v>
-      </c>
-      <c r="G26">
-        <v>16.07096201076449</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>27.571072319202</v>
+      </c>
+      <c r="C27">
         <v>40.04322527015794</v>
-      </c>
-      <c r="C27">
-        <v>27.571072319202</v>
       </c>
       <c r="D27">
         <v>2.497301336876194</v>
       </c>
       <c r="E27">
-        <v>23.8901011704027</v>
+        <v>16.44911723864313</v>
       </c>
       <c r="F27">
         <v>59.66078159095418</v>
       </c>
       <c r="G27">
-        <v>16.44911723864313</v>
+        <v>23.8901011704027</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>28.11289842120942</v>
+      </c>
+      <c r="C28">
         <v>42.01668156091748</v>
-      </c>
-      <c r="C28">
-        <v>28.11289842120942</v>
       </c>
       <c r="D28">
         <v>2.380007089684509</v>
       </c>
       <c r="E28">
-        <v>24.69687021230029</v>
+        <v>16.52440358940687</v>
       </c>
       <c r="F28">
         <v>58.77872619829284</v>
       </c>
       <c r="G28">
-        <v>16.52440358940687</v>
+        <v>24.69687021230029</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>29.94252693068685</v>
+      </c>
+      <c r="C29">
         <v>37.30724537545932</v>
-      </c>
-      <c r="C29">
-        <v>29.94252693068685</v>
       </c>
       <c r="D29">
         <v>2.680444481858742</v>
       </c>
       <c r="E29">
-        <v>22.30630562962406</v>
+        <v>17.90288053479551</v>
       </c>
       <c r="F29">
-        <v>59.79081383558042</v>
+        <v>59.79081383558043</v>
       </c>
       <c r="G29">
-        <v>17.90288053479551</v>
+        <v>22.30630562962407</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>28.44968268359021</v>
+      </c>
+      <c r="C30">
         <v>41.84950135992747</v>
-      </c>
-      <c r="C30">
-        <v>28.44968268359021</v>
       </c>
       <c r="D30">
         <v>2.389514731369151</v>
       </c>
       <c r="E30">
-        <v>24.57410562180579</v>
+        <v>16.70570698466781</v>
       </c>
       <c r="F30">
-        <v>58.7201873935264</v>
+        <v>58.72018739352641</v>
       </c>
       <c r="G30">
-        <v>16.7057069846678</v>
+        <v>24.5741056218058</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>27.50261858446805</v>
+      </c>
+      <c r="C31">
         <v>36.95196767918599</v>
-      </c>
-      <c r="C31">
-        <v>27.50261858446805</v>
       </c>
       <c r="D31">
         <v>2.706215833164608</v>
       </c>
       <c r="E31">
-        <v>22.4694053955689</v>
+        <v>16.72353396114827</v>
       </c>
       <c r="F31">
         <v>60.80706064328283</v>
       </c>
       <c r="G31">
-        <v>16.72353396114827</v>
+        <v>22.4694053955689</v>
       </c>
     </row>
   </sheetData>
